--- a/papeles_trabajo/PT_Tesoreria_2023_20251116.xlsx
+++ b/papeles_trabajo/PT_Tesoreria_2023_20251116.xlsx
@@ -60,13 +60,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -492,30 +491,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5700</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Bancos</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>7000</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
